--- a/Team-Data/2013-14/2-22-2013-14.xlsx
+++ b/Team-Data/2013-14/2-22-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,64 +728,64 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F2" t="n">
         <v>29</v>
       </c>
       <c r="G2" t="n">
-        <v>0.473</v>
+        <v>0.463</v>
       </c>
       <c r="H2" t="n">
         <v>48.5</v>
       </c>
       <c r="I2" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="J2" t="n">
-        <v>82.09999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="K2" t="n">
         <v>0.459</v>
       </c>
       <c r="L2" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="N2" t="n">
-        <v>0.377</v>
+        <v>0.374</v>
       </c>
       <c r="O2" t="n">
-        <v>16.8</v>
+        <v>16.6</v>
       </c>
       <c r="P2" t="n">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.778</v>
+        <v>0.777</v>
       </c>
       <c r="R2" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="S2" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="T2" t="n">
         <v>40.7</v>
       </c>
       <c r="U2" t="n">
-        <v>25.4</v>
+        <v>25.5</v>
       </c>
       <c r="V2" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W2" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X2" t="n">
         <v>4.3</v>
@@ -727,19 +794,19 @@
         <v>4.7</v>
       </c>
       <c r="Z2" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="AB2" t="n">
-        <v>101.5</v>
+        <v>101.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE2" t="n">
         <v>17</v>
@@ -748,7 +815,7 @@
         <v>17</v>
       </c>
       <c r="AG2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AH2" t="n">
         <v>10</v>
@@ -757,37 +824,37 @@
         <v>15</v>
       </c>
       <c r="AJ2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK2" t="n">
         <v>7</v>
       </c>
       <c r="AL2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AM2" t="n">
         <v>3</v>
       </c>
       <c r="AN2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ2" t="n">
         <v>7</v>
       </c>
       <c r="AR2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS2" t="n">
         <v>18</v>
       </c>
       <c r="AT2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AU2" t="n">
         <v>1</v>
@@ -796,7 +863,7 @@
         <v>21</v>
       </c>
       <c r="AW2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX2" t="n">
         <v>23</v>
@@ -814,7 +881,7 @@
         <v>12</v>
       </c>
       <c r="BC2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-22-2013-14</t>
+          <t>2014-02-22</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E3" t="n">
         <v>19</v>
       </c>
       <c r="F3" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G3" t="n">
-        <v>0.333</v>
+        <v>0.339</v>
       </c>
       <c r="H3" t="n">
         <v>48.1</v>
@@ -861,10 +928,10 @@
         <v>36.3</v>
       </c>
       <c r="J3" t="n">
-        <v>83.59999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="K3" t="n">
-        <v>0.434</v>
+        <v>0.435</v>
       </c>
       <c r="L3" t="n">
         <v>6.4</v>
@@ -873,31 +940,31 @@
         <v>19.6</v>
       </c>
       <c r="N3" t="n">
-        <v>0.327</v>
+        <v>0.328</v>
       </c>
       <c r="O3" t="n">
-        <v>16.1</v>
+        <v>15.9</v>
       </c>
       <c r="P3" t="n">
-        <v>21.1</v>
+        <v>20.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.762</v>
+        <v>0.765</v>
       </c>
       <c r="R3" t="n">
         <v>11.6</v>
       </c>
       <c r="S3" t="n">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="T3" t="n">
         <v>43.2</v>
       </c>
       <c r="U3" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="V3" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W3" t="n">
         <v>7.2</v>
@@ -912,16 +979,16 @@
         <v>21.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>95.09999999999999</v>
+        <v>95</v>
       </c>
       <c r="AC3" t="n">
         <v>-3.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE3" t="n">
         <v>24</v>
@@ -930,13 +997,13 @@
         <v>27</v>
       </c>
       <c r="AG3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH3" t="n">
         <v>29</v>
       </c>
       <c r="AI3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ3" t="n">
         <v>11</v>
@@ -960,7 +1027,7 @@
         <v>26</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR3" t="n">
         <v>11</v>
@@ -975,13 +1042,13 @@
         <v>26</v>
       </c>
       <c r="AV3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY3" t="n">
         <v>12</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-22-2013-14</t>
+          <t>2014-02-22</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E4" t="n">
         <v>25</v>
       </c>
       <c r="F4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>0.472</v>
+        <v>0.481</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
@@ -1046,16 +1113,16 @@
         <v>78.3</v>
       </c>
       <c r="K4" t="n">
-        <v>0.45</v>
+        <v>0.451</v>
       </c>
       <c r="L4" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="M4" t="n">
         <v>21.9</v>
       </c>
       <c r="N4" t="n">
-        <v>0.362</v>
+        <v>0.367</v>
       </c>
       <c r="O4" t="n">
         <v>18.7</v>
@@ -1064,19 +1131,19 @@
         <v>24.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.762</v>
+        <v>0.761</v>
       </c>
       <c r="R4" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="S4" t="n">
-        <v>30</v>
+        <v>29.9</v>
       </c>
       <c r="T4" t="n">
         <v>39</v>
       </c>
       <c r="U4" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="V4" t="n">
         <v>14.4</v>
@@ -1091,28 +1158,28 @@
         <v>4.1</v>
       </c>
       <c r="Z4" t="n">
-        <v>21.9</v>
+        <v>22.1</v>
       </c>
       <c r="AA4" t="n">
         <v>20.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>97.2</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2.2</v>
+        <v>-2.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF4" t="n">
         <v>14</v>
       </c>
       <c r="AG4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AH4" t="n">
         <v>8</v>
@@ -1124,10 +1191,10 @@
         <v>29</v>
       </c>
       <c r="AK4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AL4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AM4" t="n">
         <v>14</v>
@@ -1142,10 +1209,10 @@
         <v>8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AR4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS4" t="n">
         <v>27</v>
@@ -1154,22 +1221,22 @@
         <v>29</v>
       </c>
       <c r="AU4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV4" t="n">
         <v>10</v>
       </c>
       <c r="AW4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY4" t="n">
         <v>8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BA4" t="n">
         <v>11</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-22-2013-14</t>
+          <t>2014-02-22</t>
         </is>
       </c>
     </row>
@@ -1207,28 +1274,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F5" t="n">
         <v>30</v>
       </c>
       <c r="G5" t="n">
-        <v>0.474</v>
+        <v>0.464</v>
       </c>
       <c r="H5" t="n">
         <v>48.4</v>
       </c>
       <c r="I5" t="n">
-        <v>35.6</v>
+        <v>35.7</v>
       </c>
       <c r="J5" t="n">
-        <v>81.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0.437</v>
+        <v>0.438</v>
       </c>
       <c r="L5" t="n">
         <v>5.8</v>
@@ -1237,16 +1304,16 @@
         <v>16.4</v>
       </c>
       <c r="N5" t="n">
-        <v>0.354</v>
+        <v>0.353</v>
       </c>
       <c r="O5" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="P5" t="n">
         <v>25.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.726</v>
+        <v>0.723</v>
       </c>
       <c r="R5" t="n">
         <v>9.1</v>
@@ -1255,19 +1322,19 @@
         <v>33.2</v>
       </c>
       <c r="T5" t="n">
-        <v>42.2</v>
+        <v>42.3</v>
       </c>
       <c r="U5" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="V5" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="W5" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="X5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y5" t="n">
         <v>5.4</v>
@@ -1279,13 +1346,13 @@
         <v>21.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>95.2</v>
+        <v>95.3</v>
       </c>
       <c r="AC5" t="n">
         <v>-1.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE5" t="n">
         <v>14</v>
@@ -1294,7 +1361,7 @@
         <v>19</v>
       </c>
       <c r="AG5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH5" t="n">
         <v>18</v>
@@ -1306,7 +1373,7 @@
         <v>24</v>
       </c>
       <c r="AK5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL5" t="n">
         <v>29</v>
@@ -1315,7 +1382,7 @@
         <v>28</v>
       </c>
       <c r="AN5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AO5" t="n">
         <v>12</v>
@@ -1327,7 +1394,7 @@
         <v>26</v>
       </c>
       <c r="AR5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AS5" t="n">
         <v>7</v>
@@ -1345,7 +1412,7 @@
         <v>29</v>
       </c>
       <c r="AX5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY5" t="n">
         <v>21</v>
@@ -1354,7 +1421,7 @@
         <v>3</v>
       </c>
       <c r="BA5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB5" t="n">
         <v>25</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-22-2013-14</t>
+          <t>2014-02-22</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>0.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
@@ -1509,7 +1576,7 @@
         <v>10</v>
       </c>
       <c r="AR6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS6" t="n">
         <v>12</v>
@@ -1536,7 +1603,7 @@
         <v>6</v>
       </c>
       <c r="BA6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB6" t="n">
         <v>29</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-22-2013-14</t>
+          <t>2014-02-22</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-4.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
         <v>22</v>
@@ -1664,7 +1731,7 @@
         <v>2</v>
       </c>
       <c r="AI7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ7" t="n">
         <v>5</v>
@@ -1694,7 +1761,7 @@
         <v>2</v>
       </c>
       <c r="AS7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-22-2013-14</t>
+          <t>2014-02-22</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E8" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F8" t="n">
         <v>23</v>
       </c>
       <c r="G8" t="n">
-        <v>0.596</v>
+        <v>0.589</v>
       </c>
       <c r="H8" t="n">
         <v>48.1</v>
@@ -1771,7 +1838,7 @@
         <v>39.4</v>
       </c>
       <c r="J8" t="n">
-        <v>83.40000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="K8" t="n">
         <v>0.473</v>
@@ -1783,7 +1850,7 @@
         <v>22.2</v>
       </c>
       <c r="N8" t="n">
-        <v>0.375</v>
+        <v>0.376</v>
       </c>
       <c r="O8" t="n">
         <v>17.2</v>
@@ -1795,22 +1862,22 @@
         <v>0.801</v>
       </c>
       <c r="R8" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="S8" t="n">
-        <v>30.6</v>
+        <v>30.5</v>
       </c>
       <c r="T8" t="n">
-        <v>40.6</v>
+        <v>40.4</v>
       </c>
       <c r="U8" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="V8" t="n">
         <v>13.7</v>
       </c>
       <c r="W8" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X8" t="n">
         <v>4.2</v>
@@ -1825,13 +1892,13 @@
         <v>19.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>104.4</v>
+        <v>104.3</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE8" t="n">
         <v>8</v>
@@ -1861,13 +1928,13 @@
         <v>11</v>
       </c>
       <c r="AN8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO8" t="n">
         <v>16</v>
       </c>
       <c r="AP8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ8" t="n">
         <v>3</v>
@@ -1888,7 +1955,7 @@
         <v>4</v>
       </c>
       <c r="AW8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX8" t="n">
         <v>24</v>
@@ -1897,13 +1964,13 @@
         <v>3</v>
       </c>
       <c r="AZ8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC8" t="n">
         <v>12</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-22-2013-14</t>
+          <t>2014-02-22</t>
         </is>
       </c>
     </row>
@@ -2013,16 +2080,16 @@
         <v>-1.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="AE9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF9" t="n">
         <v>17</v>
       </c>
       <c r="AG9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH9" t="n">
         <v>27</v>
@@ -2034,7 +2101,7 @@
         <v>7</v>
       </c>
       <c r="AK9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL9" t="n">
         <v>9</v>
@@ -2049,7 +2116,7 @@
         <v>8</v>
       </c>
       <c r="AP9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AQ9" t="n">
         <v>27</v>
@@ -2058,7 +2125,7 @@
         <v>5</v>
       </c>
       <c r="AS9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AT9" t="n">
         <v>6</v>
@@ -2067,7 +2134,7 @@
         <v>13</v>
       </c>
       <c r="AV9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW9" t="n">
         <v>24</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-22-2013-14</t>
+          <t>2014-02-22</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E10" t="n">
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G10" t="n">
-        <v>0.411</v>
+        <v>0.418</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
@@ -2135,67 +2202,67 @@
         <v>38.8</v>
       </c>
       <c r="J10" t="n">
-        <v>86.2</v>
+        <v>86.3</v>
       </c>
       <c r="K10" t="n">
-        <v>0.45</v>
+        <v>0.449</v>
       </c>
       <c r="L10" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="M10" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="N10" t="n">
-        <v>0.312</v>
+        <v>0.313</v>
       </c>
       <c r="O10" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="P10" t="n">
-        <v>26</v>
+        <v>25.9</v>
       </c>
       <c r="Q10" t="n">
         <v>0.662</v>
       </c>
       <c r="R10" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="S10" t="n">
         <v>30.5</v>
       </c>
       <c r="T10" t="n">
-        <v>45</v>
+        <v>45.1</v>
       </c>
       <c r="U10" t="n">
         <v>20.7</v>
       </c>
       <c r="V10" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W10" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="X10" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y10" t="n">
         <v>4.7</v>
       </c>
       <c r="Z10" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AB10" t="n">
         <v>100.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>-2.4</v>
+        <v>-2.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE10" t="n">
         <v>20</v>
@@ -2219,7 +2286,7 @@
         <v>16</v>
       </c>
       <c r="AL10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM10" t="n">
         <v>25</v>
@@ -2228,10 +2295,10 @@
         <v>29</v>
       </c>
       <c r="AO10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ10" t="n">
         <v>30</v>
@@ -2246,16 +2313,16 @@
         <v>8</v>
       </c>
       <c r="AU10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV10" t="n">
         <v>18</v>
       </c>
       <c r="AW10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AY10" t="n">
         <v>16</v>
@@ -2270,7 +2337,7 @@
         <v>14</v>
       </c>
       <c r="BC10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-22-2013-14</t>
+          <t>2014-02-22</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E11" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F11" t="n">
         <v>22</v>
       </c>
       <c r="G11" t="n">
-        <v>0.607</v>
+        <v>0.6</v>
       </c>
       <c r="H11" t="n">
         <v>48.4</v>
@@ -2320,64 +2387,64 @@
         <v>85.09999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="L11" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M11" t="n">
         <v>24.2</v>
       </c>
       <c r="N11" t="n">
-        <v>0.378</v>
+        <v>0.38</v>
       </c>
       <c r="O11" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="P11" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.745</v>
+        <v>0.744</v>
       </c>
       <c r="R11" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="S11" t="n">
         <v>34.6</v>
       </c>
       <c r="T11" t="n">
-        <v>45.9</v>
+        <v>45.8</v>
       </c>
       <c r="U11" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="V11" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="W11" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="X11" t="n">
         <v>5.2</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Z11" t="n">
         <v>22</v>
       </c>
       <c r="AA11" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AB11" t="n">
-        <v>103.3</v>
+        <v>103.5</v>
       </c>
       <c r="AC11" t="n">
         <v>4.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
@@ -2389,10 +2456,10 @@
         <v>9</v>
       </c>
       <c r="AH11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ11" t="n">
         <v>6</v>
@@ -2401,16 +2468,16 @@
         <v>9</v>
       </c>
       <c r="AL11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AM11" t="n">
         <v>7</v>
       </c>
       <c r="AN11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP11" t="n">
         <v>20</v>
@@ -2431,10 +2498,10 @@
         <v>10</v>
       </c>
       <c r="AV11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AW11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX11" t="n">
         <v>9</v>
@@ -2443,7 +2510,7 @@
         <v>10</v>
       </c>
       <c r="AZ11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA11" t="n">
         <v>20</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-22-2013-14</t>
+          <t>2014-02-22</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>4.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE12" t="n">
         <v>5</v>
@@ -2571,7 +2638,7 @@
         <v>5</v>
       </c>
       <c r="AH12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AI12" t="n">
         <v>16</v>
@@ -2589,7 +2656,7 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO12" t="n">
         <v>2</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-22-2013-14</t>
+          <t>2014-02-22</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E13" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F13" t="n">
         <v>13</v>
       </c>
       <c r="G13" t="n">
-        <v>0.764</v>
+        <v>0.759</v>
       </c>
       <c r="H13" t="n">
         <v>48.3</v>
@@ -2693,34 +2760,34 @@
         <v>19.7</v>
       </c>
       <c r="N13" t="n">
-        <v>0.352</v>
+        <v>0.35</v>
       </c>
       <c r="O13" t="n">
-        <v>18.4</v>
+        <v>18.2</v>
       </c>
       <c r="P13" t="n">
-        <v>23.6</v>
+        <v>23.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.78</v>
+        <v>0.781</v>
       </c>
       <c r="R13" t="n">
         <v>10.2</v>
       </c>
       <c r="S13" t="n">
-        <v>35.2</v>
+        <v>35.3</v>
       </c>
       <c r="T13" t="n">
-        <v>45.4</v>
+        <v>45.5</v>
       </c>
       <c r="U13" t="n">
         <v>20.5</v>
       </c>
       <c r="V13" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W13" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X13" t="n">
         <v>5.7</v>
@@ -2729,19 +2796,19 @@
         <v>4.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>98.8</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE13" t="n">
         <v>2</v>
@@ -2753,7 +2820,7 @@
         <v>2</v>
       </c>
       <c r="AH13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI13" t="n">
         <v>21</v>
@@ -2771,13 +2838,13 @@
         <v>22</v>
       </c>
       <c r="AN13" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AO13" t="n">
         <v>11</v>
       </c>
       <c r="AP13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ13" t="n">
         <v>4</v>
@@ -2795,7 +2862,7 @@
         <v>24</v>
       </c>
       <c r="AV13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW13" t="n">
         <v>23</v>
@@ -2807,10 +2874,10 @@
         <v>11</v>
       </c>
       <c r="AZ13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB13" t="n">
         <v>20</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-22-2013-14</t>
+          <t>2014-02-22</t>
         </is>
       </c>
     </row>
@@ -2938,7 +3005,7 @@
         <v>23</v>
       </c>
       <c r="AI14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ14" t="n">
         <v>23</v>
@@ -2947,7 +3014,7 @@
         <v>6</v>
       </c>
       <c r="AL14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AM14" t="n">
         <v>8</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-22-2013-14</t>
+          <t>2014-02-22</t>
         </is>
       </c>
     </row>
@@ -3105,16 +3172,16 @@
         <v>-5.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE15" t="n">
         <v>24</v>
       </c>
       <c r="AF15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AH15" t="n">
         <v>28</v>
@@ -3159,7 +3226,7 @@
         <v>8</v>
       </c>
       <c r="AV15" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AW15" t="n">
         <v>28</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-22-2013-14</t>
+          <t>2014-02-22</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E16" t="n">
         <v>31</v>
       </c>
       <c r="F16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.574</v>
       </c>
       <c r="H16" t="n">
         <v>48.4</v>
@@ -3239,28 +3306,28 @@
         <v>14.2</v>
       </c>
       <c r="N16" t="n">
-        <v>0.343</v>
+        <v>0.345</v>
       </c>
       <c r="O16" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="P16" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="Q16" t="n">
         <v>0.752</v>
       </c>
       <c r="R16" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="S16" t="n">
-        <v>31</v>
+        <v>30.9</v>
       </c>
       <c r="T16" t="n">
         <v>42.4</v>
       </c>
       <c r="U16" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="V16" t="n">
         <v>13.5</v>
@@ -3272,7 +3339,7 @@
         <v>4.7</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z16" t="n">
         <v>19.7</v>
@@ -3281,19 +3348,19 @@
         <v>18.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>94.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE16" t="n">
         <v>11</v>
       </c>
       <c r="AF16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG16" t="n">
         <v>11</v>
@@ -3317,7 +3384,7 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AO16" t="n">
         <v>29</v>
@@ -3326,10 +3393,10 @@
         <v>28</v>
       </c>
       <c r="AQ16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AS16" t="n">
         <v>22</v>
@@ -3347,13 +3414,13 @@
         <v>16</v>
       </c>
       <c r="AX16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY16" t="n">
         <v>20</v>
       </c>
       <c r="AZ16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA16" t="n">
         <v>30</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-22-2013-14</t>
+          <t>2014-02-22</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3548,7 @@
         <v>3</v>
       </c>
       <c r="AH17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI17" t="n">
         <v>4</v>
@@ -3499,7 +3566,7 @@
         <v>13</v>
       </c>
       <c r="AN17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO17" t="n">
         <v>13</v>
@@ -3541,7 +3608,7 @@
         <v>12</v>
       </c>
       <c r="BB17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC17" t="n">
         <v>5</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-22-2013-14</t>
+          <t>2014-02-22</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G18" t="n">
-        <v>0.182</v>
+        <v>0.185</v>
       </c>
       <c r="H18" t="n">
         <v>48.6</v>
@@ -3597,31 +3664,31 @@
         <v>0.423</v>
       </c>
       <c r="L18" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="M18" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="N18" t="n">
         <v>0.351</v>
       </c>
       <c r="O18" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="P18" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.751</v>
+        <v>0.753</v>
       </c>
       <c r="R18" t="n">
         <v>11.5</v>
       </c>
       <c r="S18" t="n">
-        <v>29.7</v>
+        <v>29.6</v>
       </c>
       <c r="T18" t="n">
-        <v>41.3</v>
+        <v>41.1</v>
       </c>
       <c r="U18" t="n">
         <v>20.9</v>
@@ -3633,25 +3700,25 @@
         <v>6.8</v>
       </c>
       <c r="X18" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Y18" t="n">
         <v>5.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="AA18" t="n">
         <v>20.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>92.59999999999999</v>
+        <v>92.5</v>
       </c>
       <c r="AC18" t="n">
         <v>-9.300000000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3678,7 +3745,7 @@
         <v>18</v>
       </c>
       <c r="AM18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AN18" t="n">
         <v>21</v>
@@ -3690,10 +3757,10 @@
         <v>27</v>
       </c>
       <c r="AQ18" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AR18" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AS18" t="n">
         <v>29</v>
@@ -3705,19 +3772,19 @@
         <v>19</v>
       </c>
       <c r="AV18" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AW18" t="n">
         <v>27</v>
       </c>
       <c r="AX18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY18" t="n">
         <v>19</v>
       </c>
       <c r="AZ18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA18" t="n">
         <v>17</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-22-2013-14</t>
+          <t>2014-02-22</t>
         </is>
       </c>
     </row>
@@ -3755,64 +3822,64 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F19" t="n">
         <v>28</v>
       </c>
       <c r="G19" t="n">
-        <v>0.491</v>
+        <v>0.481</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
       </c>
       <c r="I19" t="n">
-        <v>38.5</v>
+        <v>38.4</v>
       </c>
       <c r="J19" t="n">
-        <v>87.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>0.438</v>
+        <v>0.437</v>
       </c>
       <c r="L19" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="M19" t="n">
         <v>21.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0.345</v>
+        <v>0.343</v>
       </c>
       <c r="O19" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="P19" t="n">
-        <v>27.2</v>
+        <v>27.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.779</v>
+        <v>0.78</v>
       </c>
       <c r="R19" t="n">
         <v>12.7</v>
       </c>
       <c r="S19" t="n">
-        <v>33.1</v>
+        <v>33</v>
       </c>
       <c r="T19" t="n">
         <v>45.7</v>
       </c>
       <c r="U19" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="V19" t="n">
         <v>13.8</v>
       </c>
       <c r="W19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="X19" t="n">
         <v>3.7</v>
@@ -3821,25 +3888,25 @@
         <v>5.7</v>
       </c>
       <c r="Z19" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="AA19" t="n">
         <v>23.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>105.7</v>
+        <v>105.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE19" t="n">
         <v>14</v>
       </c>
       <c r="AF19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG19" t="n">
         <v>14</v>
@@ -3848,13 +3915,13 @@
         <v>24</v>
       </c>
       <c r="AI19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ19" t="n">
         <v>3</v>
       </c>
       <c r="AK19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL19" t="n">
         <v>16</v>
@@ -3863,7 +3930,7 @@
         <v>12</v>
       </c>
       <c r="AN19" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AO19" t="n">
         <v>3</v>
@@ -3878,7 +3945,7 @@
         <v>4</v>
       </c>
       <c r="AS19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT19" t="n">
         <v>3</v>
@@ -3890,7 +3957,7 @@
         <v>7</v>
       </c>
       <c r="AW19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX19" t="n">
         <v>30</v>
@@ -3908,7 +3975,7 @@
         <v>4</v>
       </c>
       <c r="BC19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-22-2013-14</t>
+          <t>2014-02-22</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E20" t="n">
         <v>23</v>
       </c>
       <c r="F20" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G20" t="n">
-        <v>0.418</v>
+        <v>0.426</v>
       </c>
       <c r="H20" t="n">
         <v>48.4</v>
@@ -3958,46 +4025,46 @@
         <v>83.40000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.455</v>
+        <v>0.456</v>
       </c>
       <c r="L20" t="n">
         <v>6</v>
       </c>
       <c r="M20" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="N20" t="n">
-        <v>0.384</v>
+        <v>0.383</v>
       </c>
       <c r="O20" t="n">
         <v>17.1</v>
       </c>
       <c r="P20" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.764</v>
+        <v>0.763</v>
       </c>
       <c r="R20" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S20" t="n">
-        <v>30.3</v>
+        <v>30.4</v>
       </c>
       <c r="T20" t="n">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="U20" t="n">
         <v>21.3</v>
       </c>
       <c r="V20" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="W20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="X20" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="Y20" t="n">
         <v>6.1</v>
@@ -4009,13 +4076,13 @@
         <v>19.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>99.09999999999999</v>
+        <v>99.2</v>
       </c>
       <c r="AC20" t="n">
         <v>-1.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE20" t="n">
         <v>20</v>
@@ -4039,7 +4106,7 @@
         <v>11</v>
       </c>
       <c r="AL20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AM20" t="n">
         <v>29</v>
@@ -4048,13 +4115,13 @@
         <v>2</v>
       </c>
       <c r="AO20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP20" t="n">
         <v>18</v>
       </c>
       <c r="AQ20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR20" t="n">
         <v>7</v>
@@ -4069,7 +4136,7 @@
         <v>16</v>
       </c>
       <c r="AV20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW20" t="n">
         <v>11</v>
@@ -4084,7 +4151,7 @@
         <v>27</v>
       </c>
       <c r="BA20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BB20" t="n">
         <v>19</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-22-2013-14</t>
+          <t>2014-02-22</t>
         </is>
       </c>
     </row>
@@ -4119,25 +4186,25 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E21" t="n">
         <v>21</v>
       </c>
       <c r="F21" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G21" t="n">
-        <v>0.375</v>
+        <v>0.382</v>
       </c>
       <c r="H21" t="n">
         <v>48.6</v>
       </c>
       <c r="I21" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J21" t="n">
-        <v>83.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K21" t="n">
         <v>0.444</v>
@@ -4152,19 +4219,19 @@
         <v>0.368</v>
       </c>
       <c r="O21" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="P21" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.746</v>
+        <v>0.748</v>
       </c>
       <c r="R21" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S21" t="n">
-        <v>29.9</v>
+        <v>29.8</v>
       </c>
       <c r="T21" t="n">
         <v>40.7</v>
@@ -4173,7 +4240,7 @@
         <v>20.4</v>
       </c>
       <c r="V21" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="W21" t="n">
         <v>7.8</v>
@@ -4194,16 +4261,16 @@
         <v>97.7</v>
       </c>
       <c r="AC21" t="n">
-        <v>-1.9</v>
+        <v>-1.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE21" t="n">
         <v>23</v>
       </c>
       <c r="AF21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG21" t="n">
         <v>23</v>
@@ -4227,7 +4294,7 @@
         <v>6</v>
       </c>
       <c r="AN21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO21" t="n">
         <v>30</v>
@@ -4245,7 +4312,7 @@
         <v>28</v>
       </c>
       <c r="AT21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU21" t="n">
         <v>25</v>
@@ -4266,7 +4333,7 @@
         <v>26</v>
       </c>
       <c r="BA21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB21" t="n">
         <v>21</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-22-2013-14</t>
+          <t>2014-02-22</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>6.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4394,10 +4461,10 @@
         <v>26</v>
       </c>
       <c r="AI22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK22" t="n">
         <v>3</v>
@@ -4406,10 +4473,10 @@
         <v>17</v>
       </c>
       <c r="AM22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AN22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO22" t="n">
         <v>5</v>
@@ -4421,7 +4488,7 @@
         <v>2</v>
       </c>
       <c r="AR22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS22" t="n">
         <v>3</v>
@@ -4433,7 +4500,7 @@
         <v>14</v>
       </c>
       <c r="AV22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-22-2013-14</t>
+          <t>2014-02-22</t>
         </is>
       </c>
     </row>
@@ -4594,13 +4661,13 @@
         <v>20</v>
       </c>
       <c r="AO23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP23" t="n">
         <v>22</v>
       </c>
       <c r="AQ23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR23" t="n">
         <v>25</v>
@@ -4615,19 +4682,19 @@
         <v>20</v>
       </c>
       <c r="AV23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW23" t="n">
         <v>15</v>
       </c>
       <c r="AX23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY23" t="n">
         <v>26</v>
       </c>
       <c r="AZ23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA23" t="n">
         <v>29</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-22-2013-14</t>
+          <t>2014-02-22</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-10.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE24" t="n">
         <v>29</v>
@@ -4776,16 +4843,16 @@
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ24" t="n">
         <v>28</v>
       </c>
       <c r="AR24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AS24" t="n">
         <v>14</v>
@@ -4812,7 +4879,7 @@
         <v>22</v>
       </c>
       <c r="BA24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB24" t="n">
         <v>16</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-22-2013-14</t>
+          <t>2014-02-22</t>
         </is>
       </c>
     </row>
@@ -4925,10 +4992,10 @@
         <v>3.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="AE25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF25" t="n">
         <v>8</v>
@@ -4949,7 +5016,7 @@
         <v>8</v>
       </c>
       <c r="AL25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM25" t="n">
         <v>2</v>
@@ -4964,10 +5031,10 @@
         <v>9</v>
       </c>
       <c r="AQ25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS25" t="n">
         <v>15</v>
@@ -4991,7 +5058,7 @@
         <v>9</v>
       </c>
       <c r="AZ25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-22-2013-14</t>
+          <t>2014-02-22</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>4.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE26" t="n">
         <v>5</v>
@@ -5119,7 +5186,7 @@
         <v>5</v>
       </c>
       <c r="AH26" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AI26" t="n">
         <v>2</v>
@@ -5128,16 +5195,16 @@
         <v>2</v>
       </c>
       <c r="AK26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM26" t="n">
         <v>5</v>
       </c>
       <c r="AN26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO26" t="n">
         <v>6</v>
@@ -5161,7 +5228,7 @@
         <v>4</v>
       </c>
       <c r="AV26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW26" t="n">
         <v>30</v>
@@ -5182,7 +5249,7 @@
         <v>1</v>
       </c>
       <c r="BC26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-22-2013-14</t>
+          <t>2014-02-22</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F27" t="n">
         <v>36</v>
       </c>
       <c r="G27" t="n">
-        <v>0.345</v>
+        <v>0.333</v>
       </c>
       <c r="H27" t="n">
         <v>48.5</v>
@@ -5229,55 +5296,55 @@
         <v>37.1</v>
       </c>
       <c r="J27" t="n">
-        <v>82.90000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>0.447</v>
+        <v>0.446</v>
       </c>
       <c r="L27" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="M27" t="n">
-        <v>19.2</v>
+        <v>19.4</v>
       </c>
       <c r="N27" t="n">
-        <v>0.345</v>
+        <v>0.344</v>
       </c>
       <c r="O27" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="P27" t="n">
         <v>26.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.776</v>
+        <v>0.775</v>
       </c>
       <c r="R27" t="n">
-        <v>11.9</v>
+        <v>12.1</v>
       </c>
       <c r="S27" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="T27" t="n">
-        <v>43.7</v>
+        <v>43.8</v>
       </c>
       <c r="U27" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="V27" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W27" t="n">
         <v>7.2</v>
       </c>
       <c r="X27" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Y27" t="n">
         <v>5.6</v>
       </c>
       <c r="Z27" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="AA27" t="n">
         <v>22.6</v>
@@ -5286,19 +5353,19 @@
         <v>101.1</v>
       </c>
       <c r="AC27" t="n">
-        <v>-2.2</v>
+        <v>-2.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE27" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AF27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG27" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AH27" t="n">
         <v>10</v>
@@ -5310,10 +5377,10 @@
         <v>15</v>
       </c>
       <c r="AK27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AM27" t="n">
         <v>24</v>
@@ -5328,13 +5395,13 @@
         <v>4</v>
       </c>
       <c r="AQ27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR27" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AS27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT27" t="n">
         <v>12</v>
@@ -5346,7 +5413,7 @@
         <v>16</v>
       </c>
       <c r="AW27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX27" t="n">
         <v>29</v>
@@ -5364,7 +5431,7 @@
         <v>13</v>
       </c>
       <c r="BC27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-22-2013-14</t>
+          <t>2014-02-22</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>5.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE28" t="n">
         <v>3</v>
@@ -5483,7 +5550,7 @@
         <v>4</v>
       </c>
       <c r="AH28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI28" t="n">
         <v>1</v>
@@ -5495,7 +5562,7 @@
         <v>2</v>
       </c>
       <c r="AL28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM28" t="n">
         <v>19</v>
@@ -5534,7 +5601,7 @@
         <v>13</v>
       </c>
       <c r="AY28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ28" t="n">
         <v>2</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-22-2013-14</t>
+          <t>2014-02-22</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>2.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE29" t="n">
         <v>12</v>
@@ -5665,7 +5732,7 @@
         <v>12</v>
       </c>
       <c r="AH29" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AI29" t="n">
         <v>25</v>
@@ -5692,10 +5759,10 @@
         <v>10</v>
       </c>
       <c r="AQ29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS29" t="n">
         <v>21</v>
@@ -5722,7 +5789,7 @@
         <v>29</v>
       </c>
       <c r="BA29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB29" t="n">
         <v>17</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-22-2013-14</t>
+          <t>2014-02-22</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E30" t="n">
         <v>19</v>
       </c>
       <c r="F30" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G30" t="n">
-        <v>0.345</v>
+        <v>0.352</v>
       </c>
       <c r="H30" t="n">
         <v>48.2</v>
@@ -5778,40 +5845,40 @@
         <v>81.3</v>
       </c>
       <c r="K30" t="n">
-        <v>0.44</v>
+        <v>0.439</v>
       </c>
       <c r="L30" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="M30" t="n">
         <v>19</v>
       </c>
       <c r="N30" t="n">
-        <v>0.349</v>
+        <v>0.352</v>
       </c>
       <c r="O30" t="n">
-        <v>16.5</v>
+        <v>16.3</v>
       </c>
       <c r="P30" t="n">
-        <v>21.9</v>
+        <v>21.6</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.752</v>
+        <v>0.753</v>
       </c>
       <c r="R30" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="S30" t="n">
         <v>30.8</v>
       </c>
       <c r="T30" t="n">
-        <v>41.7</v>
+        <v>41.8</v>
       </c>
       <c r="U30" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="V30" t="n">
-        <v>14.6</v>
+        <v>14.8</v>
       </c>
       <c r="W30" t="n">
         <v>6.9</v>
@@ -5820,7 +5887,7 @@
         <v>4.6</v>
       </c>
       <c r="Y30" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Z30" t="n">
         <v>20.8</v>
@@ -5829,13 +5896,13 @@
         <v>20.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>94.59999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AC30" t="n">
-        <v>-6.2</v>
+        <v>-6</v>
       </c>
       <c r="AD30" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE30" t="n">
         <v>24</v>
@@ -5859,25 +5926,25 @@
         <v>22</v>
       </c>
       <c r="AL30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM30" t="n">
         <v>26</v>
       </c>
       <c r="AN30" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AO30" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AP30" t="n">
         <v>21</v>
       </c>
       <c r="AQ30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS30" t="n">
         <v>23</v>
@@ -5889,22 +5956,22 @@
         <v>28</v>
       </c>
       <c r="AV30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW30" t="n">
         <v>26</v>
       </c>
       <c r="AX30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB30" t="n">
         <v>28</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-22-2013-14</t>
+          <t>2014-02-22</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F31" t="n">
         <v>28</v>
       </c>
       <c r="G31" t="n">
-        <v>0.491</v>
+        <v>0.481</v>
       </c>
       <c r="H31" t="n">
         <v>48.8</v>
@@ -5957,28 +6024,28 @@
         <v>38.1</v>
       </c>
       <c r="J31" t="n">
-        <v>84.3</v>
+        <v>84.5</v>
       </c>
       <c r="K31" t="n">
-        <v>0.452</v>
+        <v>0.451</v>
       </c>
       <c r="L31" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="M31" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="N31" t="n">
-        <v>0.379</v>
+        <v>0.382</v>
       </c>
       <c r="O31" t="n">
         <v>15.4</v>
       </c>
       <c r="P31" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.729</v>
+        <v>0.728</v>
       </c>
       <c r="R31" t="n">
         <v>10.8</v>
@@ -5993,10 +6060,10 @@
         <v>23.1</v>
       </c>
       <c r="V31" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="W31" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X31" t="n">
         <v>4.8</v>
@@ -6005,25 +6072,25 @@
         <v>4</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AA31" t="n">
         <v>19.4</v>
       </c>
       <c r="AB31" t="n">
-        <v>99.40000000000001</v>
+        <v>99.5</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE31" t="n">
         <v>14</v>
       </c>
       <c r="AF31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG31" t="n">
         <v>14</v>
@@ -6038,13 +6105,13 @@
         <v>8</v>
       </c>
       <c r="AK31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL31" t="n">
         <v>15</v>
       </c>
       <c r="AM31" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AN31" t="n">
         <v>3</v>
@@ -6065,7 +6132,7 @@
         <v>20</v>
       </c>
       <c r="AT31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU31" t="n">
         <v>9</v>
@@ -6092,7 +6159,7 @@
         <v>18</v>
       </c>
       <c r="BC31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-22-2013-14</t>
+          <t>2014-02-22</t>
         </is>
       </c>
     </row>
